--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david3F(3).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david3F(3).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="20685" windowHeight="11400"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_大卫线3层（下）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1158" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1159" uniqueCount="450">
   <si>
     <t>ID</t>
   </si>
@@ -235,6 +235,9 @@
     <t>你正对着这段口诀沉思，身侧的大卫已经忍不住打开了桌面上的第二个文件。那是一份标注着日期的录音文件，时间正是前年的今日。</t>
   </si>
   <si>
+    <t>stop</t>
+  </si>
+  <si>
     <t>bgfade(sntzm_clark3F(3)_19,1)</t>
   </si>
   <si>
@@ -259,6 +262,9 @@
     <t>“......研究表明，人类在快速眼动睡眠期间，大脑前额叶皮层的活跃度显著降低，而杏仁核与海马体的连接则趋于增强。这解释了为何梦境内容往往带有强烈的情感色彩，却缺乏逻辑连贯性.......”</t>
   </si>
   <si>
+    <t>11 enhanced the_mountain-hope-background</t>
+  </si>
+  <si>
     <t>tapeon()</t>
   </si>
   <si>
@@ -442,6 +448,9 @@
     <t>先前让你们如临大敌的，并非潜伏在柜子里的怪物或是隐藏于角落的机关。只是一个女人，一个浑身被麻绳缠绕，绑得像只粽子的女性医生。</t>
   </si>
   <si>
+    <t>16 enhanced_suspence</t>
+  </si>
+  <si>
     <t>charfadeout(L,1)&amp;bgfade(sntzm_david3F(2)_24,1)</t>
   </si>
   <si>
@@ -841,7 +850,15 @@
     <t>一人检查一侧的房间，没问题吧。</t>
   </si>
   <si>
+    <t>7 enhanced litesaturation-horror</t>
+  </si>
+  <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>loadScript(</t>
     </r>
     <r>
@@ -3197,19 +3214,22 @@
       <c r="H16" t="s">
         <v>16</v>
       </c>
+      <c r="I16" t="s">
+        <v>65</v>
+      </c>
       <c r="J16" t="s">
         <v>16</v>
       </c>
       <c r="K16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" ht="27" spans="1:12">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
@@ -3227,7 +3247,7 @@
         <v>16</v>
       </c>
       <c r="G17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H17" t="s">
         <v>16</v>
@@ -3242,15 +3262,15 @@
         <v>16</v>
       </c>
       <c r="L17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" ht="57" spans="1:12">
       <c r="A18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s">
         <v>14</v>
@@ -3265,27 +3285,27 @@
         <v>16</v>
       </c>
       <c r="G18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H18" t="s">
         <v>16</v>
       </c>
       <c r="I18" t="s">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="J18" t="s">
         <v>16</v>
       </c>
       <c r="K18" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="L18" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" ht="27" spans="1:12">
       <c r="A19" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
@@ -3303,7 +3323,7 @@
         <v>16</v>
       </c>
       <c r="G19" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H19" t="s">
         <v>16</v>
@@ -3318,12 +3338,12 @@
         <v>16</v>
       </c>
       <c r="L19" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" ht="27" spans="1:12">
       <c r="A20" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
@@ -3341,7 +3361,7 @@
         <v>16</v>
       </c>
       <c r="G20" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H20" t="s">
         <v>16</v>
@@ -3356,15 +3376,15 @@
         <v>16</v>
       </c>
       <c r="L20" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" ht="45" spans="1:12">
       <c r="A21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B21" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C21" t="s">
         <v>14</v>
@@ -3379,7 +3399,7 @@
         <v>16</v>
       </c>
       <c r="G21" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H21" t="s">
         <v>16</v>
@@ -3394,15 +3414,15 @@
         <v>16</v>
       </c>
       <c r="L21" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" ht="72" spans="1:12">
       <c r="A22" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C22" t="s">
         <v>14</v>
@@ -3417,7 +3437,7 @@
         <v>16</v>
       </c>
       <c r="G22" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H22" t="s">
         <v>16</v>
@@ -3432,12 +3452,12 @@
         <v>16</v>
       </c>
       <c r="L22" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" ht="54" spans="1:12">
       <c r="A23" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
@@ -3455,7 +3475,7 @@
         <v>16</v>
       </c>
       <c r="G23" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H23" t="s">
         <v>16</v>
@@ -3470,12 +3490,12 @@
         <v>16</v>
       </c>
       <c r="L23" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B24" t="s">
         <v>21</v>
@@ -3493,7 +3513,7 @@
         <v>16</v>
       </c>
       <c r="G24" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H24" t="s">
         <v>16</v>
@@ -3508,12 +3528,12 @@
         <v>16</v>
       </c>
       <c r="L24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" ht="27" spans="1:12">
       <c r="A25" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
@@ -3531,7 +3551,7 @@
         <v>16</v>
       </c>
       <c r="G25" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H25" t="s">
         <v>16</v>
@@ -3546,12 +3566,12 @@
         <v>16</v>
       </c>
       <c r="L25" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" ht="69" spans="1:12">
       <c r="A26" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B26" t="s">
         <v>13</v>
@@ -3569,7 +3589,7 @@
         <v>16</v>
       </c>
       <c r="G26" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H26" t="s">
         <v>16</v>
@@ -3584,12 +3604,12 @@
         <v>16</v>
       </c>
       <c r="L26" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" ht="40.5" spans="1:12">
       <c r="A27" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
@@ -3607,7 +3627,7 @@
         <v>16</v>
       </c>
       <c r="G27" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H27" t="s">
         <v>16</v>
@@ -3622,15 +3642,15 @@
         <v>16</v>
       </c>
       <c r="L27" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" ht="28.5" spans="1:12">
       <c r="A28" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B28" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C28" t="s">
         <v>14</v>
@@ -3645,7 +3665,7 @@
         <v>16</v>
       </c>
       <c r="G28" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H28" t="s">
         <v>16</v>
@@ -3660,15 +3680,15 @@
         <v>16</v>
       </c>
       <c r="L28" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B29" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C29" t="s">
         <v>14</v>
@@ -3683,7 +3703,7 @@
         <v>16</v>
       </c>
       <c r="G29" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H29" t="s">
         <v>16</v>
@@ -3698,15 +3718,15 @@
         <v>16</v>
       </c>
       <c r="L29" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B30" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C30" t="s">
         <v>14</v>
@@ -3721,7 +3741,7 @@
         <v>16</v>
       </c>
       <c r="G30" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H30" t="s">
         <v>16</v>
@@ -3736,15 +3756,15 @@
         <v>16</v>
       </c>
       <c r="L30" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31" ht="42" spans="1:12">
       <c r="A31" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B31" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C31" t="s">
         <v>14</v>
@@ -3759,7 +3779,7 @@
         <v>16</v>
       </c>
       <c r="G31" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H31" t="s">
         <v>16</v>
@@ -3774,15 +3794,15 @@
         <v>16</v>
       </c>
       <c r="L31" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="32" ht="42" spans="1:12">
       <c r="A32" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B32" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C32" t="s">
         <v>14</v>
@@ -3797,7 +3817,7 @@
         <v>16</v>
       </c>
       <c r="G32" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H32" t="s">
         <v>16</v>
@@ -3809,12 +3829,12 @@
         <v>16</v>
       </c>
       <c r="L32" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" ht="42" spans="1:12">
       <c r="A33" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
@@ -3832,27 +3852,27 @@
         <v>16</v>
       </c>
       <c r="G33" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H33" t="s">
         <v>16</v>
       </c>
       <c r="I33" t="s">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="J33" t="s">
         <v>16</v>
       </c>
       <c r="K33" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="L33" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="34" ht="54" spans="1:12">
       <c r="A34" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
@@ -3870,7 +3890,7 @@
         <v>16</v>
       </c>
       <c r="G34" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H34" t="s">
         <v>16</v>
@@ -3885,12 +3905,12 @@
         <v>16</v>
       </c>
       <c r="L34" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="35" ht="28.5" spans="1:12">
       <c r="A35" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
@@ -3908,7 +3928,7 @@
         <v>16</v>
       </c>
       <c r="G35" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H35" t="s">
         <v>16</v>
@@ -3923,12 +3943,12 @@
         <v>16</v>
       </c>
       <c r="L35" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="36" ht="30" spans="1:12">
       <c r="A36" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B36" t="s">
         <v>21</v>
@@ -3946,7 +3966,7 @@
         <v>16</v>
       </c>
       <c r="G36" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H36" t="s">
         <v>16</v>
@@ -3958,15 +3978,15 @@
         <v>16</v>
       </c>
       <c r="K36" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L36" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="37" ht="40.5" spans="1:12">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="37" ht="45" spans="1:12">
       <c r="A37" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -3984,27 +4004,27 @@
         <v>16</v>
       </c>
       <c r="G37" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H37" t="s">
         <v>16</v>
       </c>
       <c r="I37" t="s">
-        <v>16</v>
+        <v>136</v>
       </c>
       <c r="J37" t="s">
         <v>16</v>
       </c>
       <c r="K37" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="L37" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="38" ht="54" spans="1:12">
       <c r="A38" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -4022,7 +4042,7 @@
         <v>16</v>
       </c>
       <c r="G38" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="H38" t="s">
         <v>16</v>
@@ -4037,12 +4057,12 @@
         <v>16</v>
       </c>
       <c r="L38" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="39" ht="54" spans="1:12">
       <c r="A39" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
@@ -4060,7 +4080,7 @@
         <v>16</v>
       </c>
       <c r="G39" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="H39" t="s">
         <v>16</v>
@@ -4075,15 +4095,15 @@
         <v>16</v>
       </c>
       <c r="L39" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B40" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C40" t="s">
         <v>14</v>
@@ -4098,7 +4118,7 @@
         <v>16</v>
       </c>
       <c r="G40" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H40" t="s">
         <v>16</v>
@@ -4113,12 +4133,12 @@
         <v>16</v>
       </c>
       <c r="L40" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="41" ht="54" spans="1:12">
       <c r="A41" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
@@ -4136,7 +4156,7 @@
         <v>16</v>
       </c>
       <c r="G41" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="H41" t="s">
         <v>16</v>
@@ -4151,12 +4171,12 @@
         <v>16</v>
       </c>
       <c r="L41" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B42" t="s">
         <v>32</v>
@@ -4174,7 +4194,7 @@
         <v>16</v>
       </c>
       <c r="G42" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="H42" t="s">
         <v>16</v>
@@ -4189,12 +4209,12 @@
         <v>16</v>
       </c>
       <c r="L42" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="43" ht="27" spans="1:12">
       <c r="A43" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -4212,7 +4232,7 @@
         <v>16</v>
       </c>
       <c r="G43" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="H43" t="s">
         <v>16</v>
@@ -4227,12 +4247,12 @@
         <v>16</v>
       </c>
       <c r="L43" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="44" ht="54" spans="1:12">
       <c r="A44" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B44" t="s">
         <v>13</v>
@@ -4250,7 +4270,7 @@
         <v>16</v>
       </c>
       <c r="G44" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H44" t="s">
         <v>16</v>
@@ -4262,18 +4282,18 @@
         <v>16</v>
       </c>
       <c r="K44" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="L44" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="45" spans="1:12">
       <c r="A45" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B45" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C45" t="s">
         <v>14</v>
@@ -4288,7 +4308,7 @@
         <v>16</v>
       </c>
       <c r="G45" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="H45" t="s">
         <v>16</v>
@@ -4303,12 +4323,12 @@
         <v>16</v>
       </c>
       <c r="L45" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="46" ht="54" spans="1:12">
       <c r="A46" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B46" t="s">
         <v>13</v>
@@ -4326,7 +4346,7 @@
         <v>16</v>
       </c>
       <c r="G46" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="H46" t="s">
         <v>16</v>
@@ -4341,12 +4361,12 @@
         <v>16</v>
       </c>
       <c r="L46" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B47" t="s">
         <v>32</v>
@@ -4364,7 +4384,7 @@
         <v>16</v>
       </c>
       <c r="G47" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="H47" t="s">
         <v>16</v>
@@ -4379,12 +4399,12 @@
         <v>16</v>
       </c>
       <c r="L47" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="48" ht="69" spans="1:12">
       <c r="A48" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
@@ -4402,7 +4422,7 @@
         <v>16</v>
       </c>
       <c r="G48" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H48" t="s">
         <v>16</v>
@@ -4417,12 +4437,12 @@
         <v>16</v>
       </c>
       <c r="L48" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="49" ht="28.5" spans="1:12">
       <c r="A49" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B49" t="s">
         <v>32</v>
@@ -4440,7 +4460,7 @@
         <v>16</v>
       </c>
       <c r="G49" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="H49" t="s">
         <v>16</v>
@@ -4455,12 +4475,12 @@
         <v>16</v>
       </c>
       <c r="L49" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="50" ht="40.5" spans="1:12">
       <c r="A50" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B50" t="s">
         <v>13</v>
@@ -4478,7 +4498,7 @@
         <v>16</v>
       </c>
       <c r="G50" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H50" t="s">
         <v>16</v>
@@ -4493,12 +4513,12 @@
         <v>16</v>
       </c>
       <c r="L50" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="51" ht="40.5" spans="1:12">
       <c r="A51" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B51" t="s">
         <v>13</v>
@@ -4516,7 +4536,7 @@
         <v>16</v>
       </c>
       <c r="G51" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H51" t="s">
         <v>16</v>
@@ -4531,12 +4551,12 @@
         <v>16</v>
       </c>
       <c r="L51" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="52" ht="27" spans="1:12">
       <c r="A52" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B52" t="s">
         <v>13</v>
@@ -4554,7 +4574,7 @@
         <v>16</v>
       </c>
       <c r="G52" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="H52" t="s">
         <v>16</v>
@@ -4569,15 +4589,15 @@
         <v>16</v>
       </c>
       <c r="L52" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="53" ht="40.5" spans="1:12">
       <c r="A53" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B53" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C53" t="s">
         <v>14</v>
@@ -4592,7 +4612,7 @@
         <v>16</v>
       </c>
       <c r="G53" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="H53" t="s">
         <v>16</v>
@@ -4607,12 +4627,12 @@
         <v>16</v>
       </c>
       <c r="L53" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B54" t="s">
         <v>32</v>
@@ -4630,7 +4650,7 @@
         <v>16</v>
       </c>
       <c r="G54" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H54" t="s">
         <v>16</v>
@@ -4645,12 +4665,12 @@
         <v>16</v>
       </c>
       <c r="L54" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="55" ht="27" spans="1:12">
       <c r="A55" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
@@ -4668,7 +4688,7 @@
         <v>16</v>
       </c>
       <c r="G55" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="H55" t="s">
         <v>16</v>
@@ -4683,15 +4703,15 @@
         <v>16</v>
       </c>
       <c r="L55" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="56" ht="28.5" spans="1:12">
       <c r="A56" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B56" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C56" t="s">
         <v>14</v>
@@ -4706,7 +4726,7 @@
         <v>16</v>
       </c>
       <c r="G56" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H56" t="s">
         <v>16</v>
@@ -4721,12 +4741,12 @@
         <v>16</v>
       </c>
       <c r="L56" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="57" ht="40.5" spans="1:12">
       <c r="A57" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B57" t="s">
         <v>13</v>
@@ -4744,7 +4764,7 @@
         <v>16</v>
       </c>
       <c r="G57" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="H57" t="s">
         <v>16</v>
@@ -4759,12 +4779,12 @@
         <v>16</v>
       </c>
       <c r="L57" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="58" ht="30" spans="1:12">
       <c r="A58" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B58" t="s">
         <v>21</v>
@@ -4782,7 +4802,7 @@
         <v>16</v>
       </c>
       <c r="G58" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="H58" t="s">
         <v>16</v>
@@ -4794,18 +4814,18 @@
         <v>16</v>
       </c>
       <c r="K58" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L58" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="59" ht="30" spans="1:12">
       <c r="A59" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B59" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C59" t="s">
         <v>14</v>
@@ -4820,7 +4840,7 @@
         <v>16</v>
       </c>
       <c r="G59" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H59" t="s">
         <v>16</v>
@@ -4835,12 +4855,12 @@
         <v>26</v>
       </c>
       <c r="L59" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="60" ht="27" spans="1:12">
       <c r="A60" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -4858,7 +4878,7 @@
         <v>16</v>
       </c>
       <c r="G60" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="H60" t="s">
         <v>16</v>
@@ -4873,12 +4893,12 @@
         <v>16</v>
       </c>
       <c r="L60" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="61" ht="54" spans="1:12">
       <c r="A61" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B61" t="s">
         <v>13</v>
@@ -4896,7 +4916,7 @@
         <v>16</v>
       </c>
       <c r="G61" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="H61" t="s">
         <v>16</v>
@@ -4911,12 +4931,12 @@
         <v>16</v>
       </c>
       <c r="L61" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="62" ht="43.5" spans="1:12">
       <c r="A62" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B62" t="s">
         <v>32</v>
@@ -4934,7 +4954,7 @@
         <v>16</v>
       </c>
       <c r="G62" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="H62" t="s">
         <v>16</v>
@@ -4949,15 +4969,15 @@
         <v>16</v>
       </c>
       <c r="L62" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="63" spans="1:12">
       <c r="A63" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B63" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C63" t="s">
         <v>14</v>
@@ -4972,7 +4992,7 @@
         <v>16</v>
       </c>
       <c r="G63" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="H63" t="s">
         <v>16</v>
@@ -4987,12 +5007,12 @@
         <v>16</v>
       </c>
       <c r="L63" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="64" spans="1:12">
       <c r="A64" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B64" t="s">
         <v>21</v>
@@ -5010,7 +5030,7 @@
         <v>16</v>
       </c>
       <c r="G64" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="H64" t="s">
         <v>16</v>
@@ -5025,12 +5045,12 @@
         <v>16</v>
       </c>
       <c r="L64" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="65" ht="54" spans="1:12">
       <c r="A65" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -5048,7 +5068,7 @@
         <v>16</v>
       </c>
       <c r="G65" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="H65" t="s">
         <v>16</v>
@@ -5063,12 +5083,12 @@
         <v>16</v>
       </c>
       <c r="L65" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B66" t="s">
         <v>32</v>
@@ -5086,7 +5106,7 @@
         <v>16</v>
       </c>
       <c r="G66" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="H66" t="s">
         <v>16</v>
@@ -5101,12 +5121,12 @@
         <v>16</v>
       </c>
       <c r="L66" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
@@ -5124,7 +5144,7 @@
         <v>16</v>
       </c>
       <c r="G67" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="H67" t="s">
         <v>16</v>
@@ -5139,12 +5159,12 @@
         <v>16</v>
       </c>
       <c r="L67" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="68" ht="40.5" spans="1:12">
       <c r="A68" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B68" t="s">
         <v>32</v>
@@ -5162,7 +5182,7 @@
         <v>16</v>
       </c>
       <c r="G68" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="H68" t="s">
         <v>16</v>
@@ -5177,12 +5197,12 @@
         <v>16</v>
       </c>
       <c r="L68" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="69" ht="55.5" spans="1:12">
       <c r="A69" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B69" t="s">
         <v>13</v>
@@ -5200,7 +5220,7 @@
         <v>16</v>
       </c>
       <c r="G69" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="H69" t="s">
         <v>16</v>
@@ -5215,15 +5235,15 @@
         <v>16</v>
       </c>
       <c r="L69" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="70" ht="55.5" spans="1:12">
       <c r="A70" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B70" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C70" t="s">
         <v>14</v>
@@ -5238,7 +5258,7 @@
         <v>16</v>
       </c>
       <c r="G70" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="H70" t="s">
         <v>16</v>
@@ -5253,12 +5273,12 @@
         <v>16</v>
       </c>
       <c r="L70" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="71" ht="40.5" spans="1:12">
       <c r="A71" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B71" t="s">
         <v>13</v>
@@ -5276,7 +5296,7 @@
         <v>16</v>
       </c>
       <c r="G71" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="H71" t="s">
         <v>16</v>
@@ -5291,12 +5311,12 @@
         <v>16</v>
       </c>
       <c r="L71" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="72" ht="57" spans="1:12">
       <c r="A72" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
@@ -5314,7 +5334,7 @@
         <v>16</v>
       </c>
       <c r="G72" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="H72" t="s">
         <v>16</v>
@@ -5326,15 +5346,15 @@
         <v>16</v>
       </c>
       <c r="K72" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="L72" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="73" ht="54" spans="1:12">
       <c r="A73" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B73" t="s">
         <v>21</v>
@@ -5352,7 +5372,7 @@
         <v>16</v>
       </c>
       <c r="G73" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="H73" t="s">
         <v>16</v>
@@ -5364,18 +5384,18 @@
         <v>16</v>
       </c>
       <c r="K73" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L73" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="74" ht="55.5" spans="1:12">
       <c r="A74" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B74" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C74" t="s">
         <v>14</v>
@@ -5387,10 +5407,10 @@
         <v>16</v>
       </c>
       <c r="F74" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="G74" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="H74" t="s">
         <v>16</v>
@@ -5402,15 +5422,15 @@
         <v>16</v>
       </c>
       <c r="K74" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="L74" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="75" ht="30" spans="1:12">
       <c r="A75" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -5425,10 +5445,10 @@
         <v>16</v>
       </c>
       <c r="F75" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="G75" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="H75" t="s">
         <v>16</v>
@@ -5440,15 +5460,15 @@
         <v>16</v>
       </c>
       <c r="K75" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="L75" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="76" ht="55.5" spans="1:12">
       <c r="A76" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B76" t="s">
         <v>13</v>
@@ -5466,7 +5486,7 @@
         <v>16</v>
       </c>
       <c r="G76" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="H76" t="s">
         <v>16</v>
@@ -5481,12 +5501,12 @@
         <v>16</v>
       </c>
       <c r="L76" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="77" ht="55.5" spans="1:12">
       <c r="A77" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
@@ -5504,7 +5524,7 @@
         <v>16</v>
       </c>
       <c r="G77" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="H77" t="s">
         <v>16</v>
@@ -5519,12 +5539,12 @@
         <v>16</v>
       </c>
       <c r="L77" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="78" ht="27" spans="1:12">
       <c r="A78" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
@@ -5542,27 +5562,27 @@
         <v>16</v>
       </c>
       <c r="G78" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="H78" t="s">
         <v>16</v>
       </c>
       <c r="I78" t="s">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="J78" t="s">
         <v>16</v>
       </c>
       <c r="K78" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="L78" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="79" ht="45" spans="1:12">
       <c r="A79" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B79" t="s">
         <v>32</v>
@@ -5580,22 +5600,22 @@
         <v>16</v>
       </c>
       <c r="G79" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="H79" t="s">
         <v>16</v>
       </c>
       <c r="I79" t="s">
-        <v>16</v>
+        <v>270</v>
       </c>
       <c r="J79" t="s">
         <v>16</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="L79" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
   </sheetData>
@@ -5616,47 +5636,47 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:2">
       <c r="A2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B3" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B4" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B5" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -5664,7 +5684,7 @@
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -5672,66 +5692,66 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B10" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B11" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B12" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B13" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B14" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B15" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -5753,616 +5773,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B2" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C2" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="D2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="E2" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="F2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B3" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="C3" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="D3" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="E3" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="F3" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B4" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C4" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="D4" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="E4" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="F4" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B5" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C5" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="D5" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E5" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="F5" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B6" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C6" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="D6" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="E6" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="F6" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B7" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C7" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="D7" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="E7" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="F7" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="C8" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D8" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="E8" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="F8" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B9" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="C9" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="D9" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="E9" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F9" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B10" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="C10" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="D10" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="E10" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="F10" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B11" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="C11" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="D11" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="E11" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="F11" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B12" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C12" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="D12" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="E12" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="F12" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B13" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C13" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D13" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="E13" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F13" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B14" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C14" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="D14" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="E14" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="F14" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B15" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C15" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="D15" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="E15" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="F15" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B16" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C16" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="D16" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="E16" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="F16" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B17" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="C17" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="D17" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E17" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="F17" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B18" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="C18" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="D18" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="E18" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="F18" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B19" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C19" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="D19" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="E19" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="F19" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B20" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C20" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="D20" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E20" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="F20" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B21" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C21" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="D21" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="E21" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="F21" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B22" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C22" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="D22" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="E22" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="F22" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B23" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C23" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D23" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="E23" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="F23" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B24" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C24" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="D24" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="E24" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="F24" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="B25" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="C25" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="D25" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="E25" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="F25" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="B26" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="C26" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="D26" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="E26" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="F26" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="B27" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C27" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="D27" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="E27" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F27" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="B28" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C28" t="s">
+        <v>433</v>
+      </c>
+      <c r="D28" t="s">
         <v>429</v>
       </c>
-      <c r="D28" t="s">
-        <v>425</v>
-      </c>
       <c r="E28" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="F28" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="B29" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C29" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="D29" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="E29" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="F29" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="B30" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="C30" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="D30" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="E30" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="F30" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="B31" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="C31" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="D31" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david3F(3).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david3F(3).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="20685" windowHeight="11400"/>
+    <workbookView windowWidth="20385" windowHeight="10605"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_大卫线3层（下）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1159" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1159" uniqueCount="451">
   <si>
     <t>ID</t>
   </si>
@@ -554,6 +554,9 @@
   </si>
   <si>
     <t>你下意识地喊出了那个既熟悉又陌生的代号，脸上的表情比她见到你们时还要惊诧和讶异。一来是对她向你们隐瞒的真实身份，二来是没想到一直在暗中以“联络员”身份和你们通讯的人，竟然就藏在这家医院里。</t>
+  </si>
+  <si>
+    <t>unlockscene(scene3)</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=46</t>
@@ -4434,15 +4437,15 @@
         <v>16</v>
       </c>
       <c r="K48" t="s">
-        <v>16</v>
+        <v>172</v>
       </c>
       <c r="L48" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="49" ht="28.5" spans="1:12">
       <c r="A49" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B49" t="s">
         <v>32</v>
@@ -4460,7 +4463,7 @@
         <v>16</v>
       </c>
       <c r="G49" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H49" t="s">
         <v>16</v>
@@ -4475,12 +4478,12 @@
         <v>16</v>
       </c>
       <c r="L49" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="50" ht="40.5" spans="1:12">
       <c r="A50" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B50" t="s">
         <v>13</v>
@@ -4498,7 +4501,7 @@
         <v>16</v>
       </c>
       <c r="G50" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H50" t="s">
         <v>16</v>
@@ -4513,12 +4516,12 @@
         <v>16</v>
       </c>
       <c r="L50" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="51" ht="40.5" spans="1:12">
       <c r="A51" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B51" t="s">
         <v>13</v>
@@ -4536,7 +4539,7 @@
         <v>16</v>
       </c>
       <c r="G51" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H51" t="s">
         <v>16</v>
@@ -4551,12 +4554,12 @@
         <v>16</v>
       </c>
       <c r="L51" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="52" ht="27" spans="1:12">
       <c r="A52" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B52" t="s">
         <v>13</v>
@@ -4574,7 +4577,7 @@
         <v>16</v>
       </c>
       <c r="G52" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H52" t="s">
         <v>16</v>
@@ -4589,12 +4592,12 @@
         <v>16</v>
       </c>
       <c r="L52" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="53" ht="40.5" spans="1:12">
       <c r="A53" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B53" t="s">
         <v>87</v>
@@ -4612,7 +4615,7 @@
         <v>16</v>
       </c>
       <c r="G53" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H53" t="s">
         <v>16</v>
@@ -4627,12 +4630,12 @@
         <v>16</v>
       </c>
       <c r="L53" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B54" t="s">
         <v>32</v>
@@ -4650,7 +4653,7 @@
         <v>16</v>
       </c>
       <c r="G54" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H54" t="s">
         <v>16</v>
@@ -4665,12 +4668,12 @@
         <v>16</v>
       </c>
       <c r="L54" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="55" ht="27" spans="1:12">
       <c r="A55" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
@@ -4688,7 +4691,7 @@
         <v>16</v>
       </c>
       <c r="G55" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H55" t="s">
         <v>16</v>
@@ -4703,12 +4706,12 @@
         <v>16</v>
       </c>
       <c r="L55" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="56" ht="28.5" spans="1:12">
       <c r="A56" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B56" t="s">
         <v>87</v>
@@ -4726,7 +4729,7 @@
         <v>16</v>
       </c>
       <c r="G56" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H56" t="s">
         <v>16</v>
@@ -4741,12 +4744,12 @@
         <v>16</v>
       </c>
       <c r="L56" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="57" ht="40.5" spans="1:12">
       <c r="A57" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B57" t="s">
         <v>13</v>
@@ -4764,7 +4767,7 @@
         <v>16</v>
       </c>
       <c r="G57" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H57" t="s">
         <v>16</v>
@@ -4779,12 +4782,12 @@
         <v>16</v>
       </c>
       <c r="L57" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="58" ht="30" spans="1:12">
       <c r="A58" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B58" t="s">
         <v>21</v>
@@ -4802,7 +4805,7 @@
         <v>16</v>
       </c>
       <c r="G58" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H58" t="s">
         <v>16</v>
@@ -4817,12 +4820,12 @@
         <v>132</v>
       </c>
       <c r="L58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" ht="30" spans="1:12">
       <c r="A59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B59" t="s">
         <v>87</v>
@@ -4840,7 +4843,7 @@
         <v>16</v>
       </c>
       <c r="G59" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H59" t="s">
         <v>16</v>
@@ -4855,12 +4858,12 @@
         <v>26</v>
       </c>
       <c r="L59" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="60" ht="27" spans="1:12">
       <c r="A60" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -4878,7 +4881,7 @@
         <v>16</v>
       </c>
       <c r="G60" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H60" t="s">
         <v>16</v>
@@ -4893,12 +4896,12 @@
         <v>16</v>
       </c>
       <c r="L60" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="61" ht="54" spans="1:12">
       <c r="A61" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B61" t="s">
         <v>13</v>
@@ -4916,7 +4919,7 @@
         <v>16</v>
       </c>
       <c r="G61" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H61" t="s">
         <v>16</v>
@@ -4931,12 +4934,12 @@
         <v>16</v>
       </c>
       <c r="L61" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="62" ht="43.5" spans="1:12">
       <c r="A62" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B62" t="s">
         <v>32</v>
@@ -4954,7 +4957,7 @@
         <v>16</v>
       </c>
       <c r="G62" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H62" t="s">
         <v>16</v>
@@ -4969,12 +4972,12 @@
         <v>16</v>
       </c>
       <c r="L62" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="63" spans="1:12">
       <c r="A63" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B63" t="s">
         <v>87</v>
@@ -4992,7 +4995,7 @@
         <v>16</v>
       </c>
       <c r="G63" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H63" t="s">
         <v>16</v>
@@ -5007,12 +5010,12 @@
         <v>16</v>
       </c>
       <c r="L63" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="64" spans="1:12">
       <c r="A64" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B64" t="s">
         <v>21</v>
@@ -5030,7 +5033,7 @@
         <v>16</v>
       </c>
       <c r="G64" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H64" t="s">
         <v>16</v>
@@ -5045,12 +5048,12 @@
         <v>16</v>
       </c>
       <c r="L64" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="65" ht="54" spans="1:12">
       <c r="A65" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -5068,7 +5071,7 @@
         <v>16</v>
       </c>
       <c r="G65" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H65" t="s">
         <v>16</v>
@@ -5083,12 +5086,12 @@
         <v>16</v>
       </c>
       <c r="L65" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B66" t="s">
         <v>32</v>
@@ -5106,7 +5109,7 @@
         <v>16</v>
       </c>
       <c r="G66" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H66" t="s">
         <v>16</v>
@@ -5121,12 +5124,12 @@
         <v>16</v>
       </c>
       <c r="L66" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
@@ -5144,7 +5147,7 @@
         <v>16</v>
       </c>
       <c r="G67" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H67" t="s">
         <v>16</v>
@@ -5159,12 +5162,12 @@
         <v>16</v>
       </c>
       <c r="L67" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="68" ht="40.5" spans="1:12">
       <c r="A68" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B68" t="s">
         <v>32</v>
@@ -5182,7 +5185,7 @@
         <v>16</v>
       </c>
       <c r="G68" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H68" t="s">
         <v>16</v>
@@ -5197,12 +5200,12 @@
         <v>16</v>
       </c>
       <c r="L68" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="69" ht="55.5" spans="1:12">
       <c r="A69" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B69" t="s">
         <v>13</v>
@@ -5220,7 +5223,7 @@
         <v>16</v>
       </c>
       <c r="G69" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H69" t="s">
         <v>16</v>
@@ -5235,12 +5238,12 @@
         <v>16</v>
       </c>
       <c r="L69" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="70" ht="55.5" spans="1:12">
       <c r="A70" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B70" t="s">
         <v>87</v>
@@ -5258,7 +5261,7 @@
         <v>16</v>
       </c>
       <c r="G70" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H70" t="s">
         <v>16</v>
@@ -5273,12 +5276,12 @@
         <v>16</v>
       </c>
       <c r="L70" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="71" ht="40.5" spans="1:12">
       <c r="A71" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B71" t="s">
         <v>13</v>
@@ -5296,7 +5299,7 @@
         <v>16</v>
       </c>
       <c r="G71" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H71" t="s">
         <v>16</v>
@@ -5311,12 +5314,12 @@
         <v>16</v>
       </c>
       <c r="L71" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="72" ht="57" spans="1:12">
       <c r="A72" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
@@ -5334,7 +5337,7 @@
         <v>16</v>
       </c>
       <c r="G72" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H72" t="s">
         <v>16</v>
@@ -5346,15 +5349,15 @@
         <v>16</v>
       </c>
       <c r="K72" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L72" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="73" ht="54" spans="1:12">
       <c r="A73" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B73" t="s">
         <v>21</v>
@@ -5372,7 +5375,7 @@
         <v>16</v>
       </c>
       <c r="G73" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H73" t="s">
         <v>16</v>
@@ -5387,12 +5390,12 @@
         <v>132</v>
       </c>
       <c r="L73" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="74" ht="55.5" spans="1:12">
       <c r="A74" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B74" t="s">
         <v>87</v>
@@ -5407,10 +5410,10 @@
         <v>16</v>
       </c>
       <c r="F74" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G74" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H74" t="s">
         <v>16</v>
@@ -5422,15 +5425,15 @@
         <v>16</v>
       </c>
       <c r="K74" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L74" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="75" ht="30" spans="1:12">
       <c r="A75" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -5445,10 +5448,10 @@
         <v>16</v>
       </c>
       <c r="F75" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G75" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H75" t="s">
         <v>16</v>
@@ -5460,15 +5463,15 @@
         <v>16</v>
       </c>
       <c r="K75" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L75" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="76" ht="55.5" spans="1:12">
       <c r="A76" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B76" t="s">
         <v>13</v>
@@ -5486,7 +5489,7 @@
         <v>16</v>
       </c>
       <c r="G76" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H76" t="s">
         <v>16</v>
@@ -5501,12 +5504,12 @@
         <v>16</v>
       </c>
       <c r="L76" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="77" ht="55.5" spans="1:12">
       <c r="A77" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
@@ -5524,7 +5527,7 @@
         <v>16</v>
       </c>
       <c r="G77" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H77" t="s">
         <v>16</v>
@@ -5539,12 +5542,12 @@
         <v>16</v>
       </c>
       <c r="L77" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="78" ht="27" spans="1:12">
       <c r="A78" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
@@ -5562,7 +5565,7 @@
         <v>16</v>
       </c>
       <c r="G78" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H78" t="s">
         <v>16</v>
@@ -5574,15 +5577,15 @@
         <v>16</v>
       </c>
       <c r="K78" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L78" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="79" ht="45" spans="1:12">
       <c r="A79" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B79" t="s">
         <v>32</v>
@@ -5600,22 +5603,22 @@
         <v>16</v>
       </c>
       <c r="G79" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H79" t="s">
         <v>16</v>
       </c>
       <c r="I79" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J79" t="s">
         <v>16</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L79" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
   </sheetData>
@@ -5636,47 +5639,47 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:2">
       <c r="A2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -5684,7 +5687,7 @@
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -5692,7 +5695,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B8" t="s">
         <v>114</v>
@@ -5700,7 +5703,7 @@
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B9" t="s">
         <v>80</v>
@@ -5708,50 +5711,50 @@
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B11" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B12" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B13" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B14" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B15" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
   </sheetData>
@@ -5773,616 +5776,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B5" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C5" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D5" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B7" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D7" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E7" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B8" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C8" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D8" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E8" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F8" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B9" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F9" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E10" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B11" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C11" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D11" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E11" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B12" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C12" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E12" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F12" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B13" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C13" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D13" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E13" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F13" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B14" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E14" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F14" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B15" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C15" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D15" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E15" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F15" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B16" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C16" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D16" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E16" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F16" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B17" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C17" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D17" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E17" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F17" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B18" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C18" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D18" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E18" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F18" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B19" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C19" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D19" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E19" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F19" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B20" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C20" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D20" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E20" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F20" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B21" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C21" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D21" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E21" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F21" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B22" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C22" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D22" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E22" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F22" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B23" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C23" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D23" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E23" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F23" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B24" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C24" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D24" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E24" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F24" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B25" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C25" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D25" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E25" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F25" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B26" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C26" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D26" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E26" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F26" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B27" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C27" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D27" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E27" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F27" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B28" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C28" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D28" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E28" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F28" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B29" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C29" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D29" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E29" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F29" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B30" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C30" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D30" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E30" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F30" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B31" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C31" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D31" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
   </sheetData>
